--- a/ig/mc-add-link-doc/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/ig/mc-add-link-doc/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:30:52+00:00</t>
+    <t>2023-05-17T07:53:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -331,7 +331,7 @@
     <t>An Extension</t>
   </si>
   <si>
-    <t>Synonyme MOS : numeroSerie ; format de codage des caractères en binaire codé en ASCII.</t>
+    <t>Synonyme : numeroSerie ; format de codage des caractères en binaire codé en ASCII.</t>
   </si>
   <si>
     <t>Extension.extension:serialNumber.id</t>
@@ -396,7 +396,7 @@
     <t>DN (Distinguished Name - Nom distinctif) de l’autorité de certification (AC) émettrice du certificat</t>
   </si>
   <si>
-    <t>Synonyme MOS : dNEmetteur ; le format respecte le standard RFC-4514, avec un codage des caractères en UTF8</t>
+    <t>Synonyme : dNEmetteur ; le format respecte le standard RFC-4514, avec un codage des caractères en UTF8</t>
   </si>
   <si>
     <t>Extension.extension:issuer.id</t>
@@ -420,7 +420,7 @@
     <t>DN (Distinguished Name - Nom distinctif) du porteur du certificat</t>
   </si>
   <si>
-    <t>Synonyme MOS : dNSujet ; codage des caractères en UTF8</t>
+    <t>Synonyme : dNSujet ; codage des caractères en UTF8</t>
   </si>
   <si>
     <t>Extension.extension:subject.id</t>
@@ -444,7 +444,7 @@
     <t>Période de validité du certificat.</t>
   </si>
   <si>
-    <t>Synonyme MOS : periodValidite ; la date est en UTC (avec translation de l'heure locale en heure UTC par ajout du décalage négatif ou retranchement du décalage positif).</t>
+    <t>Synonyme : periodValidite ; la date est en UTC (avec translation de l'heure locale en heure UTC par ajout du décalage négatif ou retranchement du décalage positif).</t>
   </si>
   <si>
     <t>Extension.extension:validity.id</t>
@@ -507,7 +507,7 @@
     <t>The start of the period. The boundary is inclusive.</t>
   </si>
   <si>
-    <t>Synonyme MOS : dateDebutValidite</t>
+    <t>Synonyme : dateDebutValidite</t>
   </si>
   <si>
     <t>Period.start</t>
@@ -532,7 +532,7 @@
     <t>The end of the period. If the end of the period is missing, it means no end was known or planned at the time the instance was created. The start may be in the past, and the end date in the future, which means that period is expected/planned to end at that time.</t>
   </si>
   <si>
-    <t>Synonyme MOS : dateFinValidite</t>
+    <t>Synonyme : dateFinValidite</t>
   </si>
   <si>
     <t>If the end of the period is missing, it means that the period is ongoing</t>
@@ -553,7 +553,7 @@
     <t>Ce champ correspond au CN du DNSujet, il contient soit un &lt;FQDN&gt; pour les certificats de type serveur &lt;SSL&gt;, soit un nom applicatif pour les autres certificats.</t>
   </si>
   <si>
-    <t>Synonyme MOS : domaine ; renseigné uniquement pour les certificats logiciels de portée Structure.</t>
+    <t>Synonyme : domaine ; renseigné uniquement pour les certificats logiciels de portée Structure.</t>
   </si>
   <si>
     <t>Extension.extension:domain.id</t>
@@ -601,7 +601,7 @@
     <t>Valeur binaire du certificat.</t>
   </si>
   <si>
-    <t>Synonyme MOS : valeurBinaire ; format .crt en hexadécimal, codé en ASCII</t>
+    <t>Synonyme : valeurBinaire ; format .crt en hexadécimal, codé en ASCII</t>
   </si>
   <si>
     <t>Extension.extension:value.id</t>
